--- a/386-création-onglet-problématiques-connues/ig/StructureDefinition-tddui-exit-mode-label.xlsx
+++ b/386-création-onglet-problématiques-connues/ig/StructureDefinition-tddui-exit-mode-label.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T08:26:30+00:00</t>
+    <t>2026-03-12T08:40:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/386-création-onglet-problématiques-connues/ig/StructureDefinition-tddui-exit-mode-label.xlsx
+++ b/386-création-onglet-problématiques-connues/ig/StructureDefinition-tddui-exit-mode-label.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T08:40:42+00:00</t>
+    <t>2026-03-12T10:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/386-création-onglet-problématiques-connues/ig/StructureDefinition-tddui-exit-mode-label.xlsx
+++ b/386-création-onglet-problématiques-connues/ig/StructureDefinition-tddui-exit-mode-label.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T10:41:45+00:00</t>
+    <t>2026-03-12T13:09:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/386-création-onglet-problématiques-connues/ig/StructureDefinition-tddui-exit-mode-label.xlsx
+++ b/386-création-onglet-problématiques-connues/ig/StructureDefinition-tddui-exit-mode-label.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T13:09:15+00:00</t>
+    <t>2026-03-12T16:04:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/386-création-onglet-problématiques-connues/ig/StructureDefinition-tddui-exit-mode-label.xlsx
+++ b/386-création-onglet-problématiques-connues/ig/StructureDefinition-tddui-exit-mode-label.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T16:04:53+00:00</t>
+    <t>2026-03-12T16:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/386-création-onglet-problématiques-connues/ig/StructureDefinition-tddui-exit-mode-label.xlsx
+++ b/386-création-onglet-problématiques-connues/ig/StructureDefinition-tddui-exit-mode-label.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T16:28:34+00:00</t>
+    <t>2026-03-13T13:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/386-création-onglet-problématiques-connues/ig/StructureDefinition-tddui-exit-mode-label.xlsx
+++ b/386-création-onglet-problématiques-connues/ig/StructureDefinition-tddui-exit-mode-label.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T13:28:40+00:00</t>
+    <t>2026-03-13T13:43:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
